--- a/Excels/Skill.xlsx
+++ b/Excels/Skill.xlsx
@@ -255,6 +255,7 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -846,7 +847,7 @@
         <v>2</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:14">

--- a/Excels/Skill.xlsx
+++ b/Excels/Skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11780"/>
+    <workbookView xWindow="-120" yWindow="-470" windowWidth="29000" windowHeight="12310"/>
   </bookViews>
   <sheets>
     <sheet name="SkillCfg" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="60">
   <si>
     <t>id</t>
   </si>
@@ -36,12 +36,6 @@
   </si>
   <si>
     <t>searchRange</t>
-  </si>
-  <si>
-    <t>atkRange</t>
-  </si>
-  <si>
-    <t>skillArea</t>
   </si>
   <si>
     <t>damage</t>
@@ -237,6 +231,30 @@
   </si>
   <si>
     <t>死亡方式（）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tornado</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atkRange</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bounce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skillArea</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>投石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explosion</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -563,7 +581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
@@ -586,128 +604,128 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" t="s">
-        <v>9</v>
-      </c>
       <c r="M1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" t="s">
         <v>10</v>
       </c>
-      <c r="I2" t="s">
-        <v>12</v>
-      </c>
       <c r="J2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="N2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" t="s">
+      <c r="F3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
         <v>16</v>
       </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
         <v>17</v>
       </c>
-      <c r="H3" t="s">
+      <c r="J3" t="s">
         <v>18</v>
       </c>
-      <c r="I3" t="s">
+      <c r="K3" t="s">
         <v>19</v>
       </c>
-      <c r="J3" t="s">
+      <c r="L3" t="s">
         <v>20</v>
       </c>
-      <c r="K3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3" t="s">
-        <v>22</v>
-      </c>
       <c r="M3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="N3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -715,13 +733,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E4">
         <v>50</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -750,13 +768,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E5">
         <v>150</v>
       </c>
       <c r="F5">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -785,7 +803,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E6">
         <v>50</v>
@@ -820,7 +838,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E7">
         <v>50</v>
@@ -829,13 +847,13 @@
         <v>50</v>
       </c>
       <c r="G7">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H7">
         <v>1</v>
       </c>
       <c r="I7">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -847,7 +865,10 @@
         <v>2</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -855,7 +876,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E8">
         <v>50</v>
@@ -864,7 +885,7 @@
         <v>5</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -890,7 +911,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E9">
         <v>50</v>
@@ -925,7 +946,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E10">
         <v>50</v>
@@ -960,7 +981,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E11">
         <v>50</v>
@@ -995,7 +1016,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E12">
         <v>50</v>
@@ -1030,7 +1051,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E13">
         <v>50</v>
@@ -1065,7 +1086,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E14">
         <v>50</v>
@@ -1100,7 +1121,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E15">
         <v>50</v>
@@ -1135,7 +1156,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E16">
         <v>50</v>
@@ -1165,12 +1186,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:14">
       <c r="A17">
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E17">
         <v>50</v>
@@ -1200,12 +1221,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:14">
       <c r="A18">
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E18">
         <v>50</v>
@@ -1235,12 +1256,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:14">
       <c r="A19">
         <v>16</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C19" s="1"/>
       <c r="E19">
@@ -1271,12 +1292,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:14">
       <c r="A20">
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E20">
         <v>50</v>
@@ -1306,12 +1327,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:14">
       <c r="A21">
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E21">
         <v>50</v>
@@ -1341,12 +1362,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:14">
       <c r="A22">
         <v>19</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C22" s="1"/>
       <c r="E22">
@@ -1377,12 +1398,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:14">
       <c r="A23">
         <v>20</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E23">
         <v>50</v>
@@ -1412,21 +1433,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:14">
       <c r="A24">
         <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E24">
         <v>50</v>
       </c>
       <c r="F24">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -1435,16 +1456,57 @@
         <v>2</v>
       </c>
       <c r="J24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M24">
         <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25">
+        <v>22</v>
+      </c>
+      <c r="B25" t="s">
+        <v>58</v>
+      </c>
+      <c r="E25">
+        <v>150</v>
+      </c>
+      <c r="F25">
+        <v>50</v>
+      </c>
+      <c r="G25">
+        <v>5</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25">
+        <v>2</v>
+      </c>
+      <c r="J25">
+        <v>1</v>
+      </c>
+      <c r="K25">
+        <v>2</v>
+      </c>
+      <c r="L25">
+        <v>3</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/Excels/Skill.xlsx
+++ b/Excels/Skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-470" windowWidth="29000" windowHeight="12310"/>
+    <workbookView xWindow="-170" yWindow="-690" windowWidth="29090" windowHeight="12560"/>
   </bookViews>
   <sheets>
     <sheet name="SkillCfg" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="61">
   <si>
     <t>id</t>
   </si>
@@ -38,9 +38,6 @@
     <t>searchRange</t>
   </si>
   <si>
-    <t>damage</t>
-  </si>
-  <si>
     <t>cd</t>
   </si>
   <si>
@@ -146,10 +143,6 @@
   </si>
   <si>
     <t>项庄普攻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>startEffect</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -238,23 +231,35 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>Bounce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>投石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explosion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>atkRange</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Bounce</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>skillArea</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>投石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Explosion</t>
+    <t>startEffect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skillDamageRate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -604,128 +609,128 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D1" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" t="s">
         <v>3</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>4</v>
       </c>
-      <c r="J1" t="s">
-        <v>5</v>
-      </c>
       <c r="K1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" t="s">
         <v>6</v>
       </c>
-      <c r="L1" t="s">
-        <v>7</v>
-      </c>
       <c r="M1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="I2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>14</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>15</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>16</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>17</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>18</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>19</v>
       </c>
-      <c r="L3" t="s">
-        <v>20</v>
-      </c>
       <c r="M3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -733,7 +738,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E4">
         <v>50</v>
@@ -768,7 +773,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E5">
         <v>150</v>
@@ -803,7 +808,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E6">
         <v>50</v>
@@ -838,7 +843,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E7">
         <v>50</v>
@@ -868,7 +873,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -876,7 +881,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E8">
         <v>50</v>
@@ -911,7 +916,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E9">
         <v>50</v>
@@ -946,7 +951,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E10">
         <v>50</v>
@@ -981,7 +986,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E11">
         <v>50</v>
@@ -1016,7 +1021,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E12">
         <v>50</v>
@@ -1051,7 +1056,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E13">
         <v>50</v>
@@ -1086,7 +1091,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E14">
         <v>50</v>
@@ -1121,7 +1126,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E15">
         <v>50</v>
@@ -1156,7 +1161,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E16">
         <v>50</v>
@@ -1191,7 +1196,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E17">
         <v>50</v>
@@ -1226,7 +1231,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E18">
         <v>50</v>
@@ -1261,7 +1266,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C19" s="1"/>
       <c r="E19">
@@ -1297,7 +1302,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E20">
         <v>50</v>
@@ -1332,7 +1337,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E21">
         <v>50</v>
@@ -1367,7 +1372,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C22" s="1"/>
       <c r="E22">
@@ -1403,7 +1408,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E23">
         <v>50</v>
@@ -1438,7 +1443,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E24">
         <v>50</v>
@@ -1468,7 +1473,7 @@
         <v>0</v>
       </c>
       <c r="N24" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1476,7 +1481,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E25">
         <v>150</v>
@@ -1506,7 +1511,7 @@
         <v>0</v>
       </c>
       <c r="N25" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/Excels/Skill.xlsx
+++ b/Excels/Skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-170" yWindow="-690" windowWidth="29090" windowHeight="12560"/>
+    <workbookView xWindow="-260" yWindow="-1010" windowWidth="29230" windowHeight="12940"/>
   </bookViews>
   <sheets>
     <sheet name="SkillCfg" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="63">
   <si>
     <t>id</t>
   </si>
@@ -147,10 +147,6 @@
   </si>
   <si>
     <t>冰风暴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>电闪雷鸣</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -251,15 +247,27 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>skillDamageRate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷霆万钧</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全局技能-投石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>startEffect</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>skillDamageRate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>float</t>
+    <t>奇门遁甲</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -586,11 +594,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
-    <col min="2" max="4" width="18.08203125" customWidth="1"/>
+    <col min="2" max="3" width="18.08203125" customWidth="1"/>
+    <col min="4" max="4" width="22.6640625" customWidth="1"/>
     <col min="5" max="6" width="19.4140625" customWidth="1"/>
     <col min="7" max="7" width="20.58203125" customWidth="1"/>
     <col min="8" max="8" width="32.83203125" customWidth="1"/>
@@ -609,22 +618,22 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="I1" t="s">
         <v>3</v>
@@ -639,10 +648,10 @@
         <v>6</v>
       </c>
       <c r="M1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -653,7 +662,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
         <v>23</v>
@@ -668,7 +677,7 @@
         <v>9</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I2" t="s">
         <v>9</v>
@@ -683,10 +692,10 @@
         <v>7</v>
       </c>
       <c r="M2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -697,7 +706,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
         <v>24</v>
@@ -727,10 +736,10 @@
         <v>19</v>
       </c>
       <c r="M3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -873,7 +882,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1231,7 +1240,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E18">
         <v>50</v>
@@ -1266,7 +1275,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19" s="1"/>
       <c r="E19">
@@ -1302,7 +1311,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E20">
         <v>50</v>
@@ -1337,7 +1346,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E21">
         <v>50</v>
@@ -1372,7 +1381,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C22" s="1"/>
       <c r="E22">
@@ -1408,7 +1417,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E23">
         <v>50</v>
@@ -1443,7 +1452,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E24">
         <v>50</v>
@@ -1473,7 +1482,7 @@
         <v>0</v>
       </c>
       <c r="N24" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1481,7 +1490,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E25">
         <v>150</v>
@@ -1511,7 +1520,80 @@
         <v>0</v>
       </c>
       <c r="N25" t="s">
-        <v>55</v>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>62</v>
+      </c>
+      <c r="E26">
+        <v>50</v>
+      </c>
+      <c r="F26">
+        <v>10</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26">
+        <v>2</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>2</v>
+      </c>
+      <c r="L26">
+        <v>5</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27">
+        <v>1001</v>
+      </c>
+      <c r="B27" t="s">
+        <v>60</v>
+      </c>
+      <c r="E27">
+        <v>1000</v>
+      </c>
+      <c r="F27">
+        <v>1000</v>
+      </c>
+      <c r="G27">
+        <v>10</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>2</v>
+      </c>
+      <c r="L27">
+        <v>10001</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/Excels/Skill.xlsx
+++ b/Excels/Skill.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="65">
   <si>
     <t>id</t>
   </si>
@@ -147,18 +147,6 @@
   </si>
   <si>
     <t>冰风暴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>飞龙在天</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>狂风箭雨</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>狂龙吼</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -191,10 +179,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>燕人咆哮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>风卷残云</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -269,6 +253,29 @@
   <si>
     <t>奇门遁甲</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>野火燎原</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effects/熊吼土黄色</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>燕人在此</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>倒转昆仑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effects/FX_金色蓝色旋转体_周身技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>裂地天刑</t>
   </si>
 </sst>
 </file>
@@ -599,7 +606,7 @@
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
     <col min="2" max="3" width="18.08203125" customWidth="1"/>
-    <col min="4" max="4" width="22.6640625" customWidth="1"/>
+    <col min="4" max="4" width="45.6640625" customWidth="1"/>
     <col min="5" max="6" width="19.4140625" customWidth="1"/>
     <col min="7" max="7" width="20.58203125" customWidth="1"/>
     <col min="8" max="8" width="32.83203125" customWidth="1"/>
@@ -618,22 +625,22 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I1" t="s">
         <v>3</v>
@@ -648,10 +655,10 @@
         <v>6</v>
       </c>
       <c r="M1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="N1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -662,7 +669,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
         <v>23</v>
@@ -677,7 +684,7 @@
         <v>9</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="I2" t="s">
         <v>9</v>
@@ -692,10 +699,10 @@
         <v>7</v>
       </c>
       <c r="M2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="N2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -706,7 +713,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
         <v>24</v>
@@ -736,10 +743,10 @@
         <v>19</v>
       </c>
       <c r="M3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="N3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -882,7 +889,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1240,34 +1247,37 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E18">
         <v>50</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H18">
         <v>1</v>
       </c>
       <c r="I18">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M18">
         <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1275,9 +1285,12 @@
         <v>16</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="C19" s="1"/>
+      <c r="D19" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="E19">
         <v>50</v>
       </c>
@@ -1285,16 +1298,16 @@
         <v>5</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H19">
         <v>1</v>
       </c>
       <c r="I19">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19">
         <v>1</v>
@@ -1304,14 +1317,17 @@
       </c>
       <c r="M19">
         <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20">
         <v>17</v>
       </c>
-      <c r="B20" t="s">
-        <v>37</v>
+      <c r="B20" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="E20">
         <v>50</v>
@@ -1326,16 +1342,16 @@
         <v>1</v>
       </c>
       <c r="I20">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M20">
         <v>0</v>
@@ -1345,29 +1361,29 @@
       <c r="A21">
         <v>18</v>
       </c>
-      <c r="B21" t="s">
-        <v>36</v>
+      <c r="B21" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="E21">
         <v>50</v>
       </c>
       <c r="F21">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H21">
         <v>1</v>
       </c>
       <c r="I21">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -1381,7 +1397,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C22" s="1"/>
       <c r="E22">
@@ -1397,10 +1413,10 @@
         <v>1</v>
       </c>
       <c r="I22">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22">
         <v>1</v>
@@ -1417,7 +1433,10 @@
         <v>20</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>43</v>
+        <v>62</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="E23">
         <v>50</v>
@@ -1426,16 +1445,16 @@
         <v>5</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H23">
         <v>1</v>
       </c>
       <c r="I23">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23">
         <v>1</v>
@@ -1452,7 +1471,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E24">
         <v>50</v>
@@ -1467,7 +1486,7 @@
         <v>1</v>
       </c>
       <c r="I24">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -1482,24 +1501,24 @@
         <v>0</v>
       </c>
       <c r="N24" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E25">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F25">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G25">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -1508,42 +1527,39 @@
         <v>2</v>
       </c>
       <c r="J25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25">
         <v>2</v>
       </c>
       <c r="L25">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M25">
         <v>0</v>
-      </c>
-      <c r="N25" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26">
-        <v>23</v>
+        <v>1001</v>
       </c>
       <c r="B26" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E26">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="F26">
+        <v>1000</v>
+      </c>
+      <c r="G26">
         <v>10</v>
       </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
       <c r="H26">
         <v>1</v>
       </c>
       <c r="I26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -1552,48 +1568,51 @@
         <v>2</v>
       </c>
       <c r="L26">
-        <v>5</v>
+        <v>10001</v>
       </c>
       <c r="M26">
         <v>0</v>
+      </c>
+      <c r="N26" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27">
-        <v>1001</v>
+        <v>22</v>
       </c>
       <c r="B27" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E27">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="F27">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="G27">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H27">
         <v>1</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27">
         <v>2</v>
       </c>
       <c r="L27">
-        <v>10001</v>
+        <v>3</v>
       </c>
       <c r="M27">
         <v>0</v>
       </c>
       <c r="N27" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/Excels/Skill.xlsx
+++ b/Excels/Skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-260" yWindow="-1010" windowWidth="29230" windowHeight="12940"/>
+    <workbookView xWindow="19270" yWindow="-10" windowWidth="19160" windowHeight="10090"/>
   </bookViews>
   <sheets>
     <sheet name="SkillCfg" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="77">
   <si>
     <t>id</t>
   </si>
@@ -179,103 +179,152 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>buffId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int[]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buff信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dieType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>死亡方式（）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tornado</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bounce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>投石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explosion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atkRange</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skillArea</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skillDamageRate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全局技能-投石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>startEffect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奇门遁甲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effects/熊吼土黄色</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effects/FX_金色蓝色旋转体_周身技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>力劈华山</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>乌云后雷电-远</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火龙追日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FX_火焰从天而降</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FX_剑落下爆炸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓝色龙卷风</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>飞剑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FX_从天而降的拳头土黄色</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>翻雷滚天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FX_红色飓风带雷电</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>万剑穿心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FX_冰箭从天而降爆炸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>裂地天刑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷霆万钧</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>燕人在此</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>倒转昆仑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>风卷残云</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>buffId</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int[]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>buff信息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dieType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>死亡方式（）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tornado</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bounce</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>投石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Explosion</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>atkRange</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>skillArea</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>skillDamageRate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>float</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>雷霆万钧</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>全局技能-投石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>startEffect</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>奇门遁甲</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>野火燎原</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effects/熊吼土黄色</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>燕人在此</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>倒转昆仑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effects/FX_金色蓝色旋转体_周身技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>裂地天刑</t>
+    <t>Squash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -326,9 +375,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -601,7 +657,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
@@ -628,19 +684,19 @@
         <v>37</v>
       </c>
       <c r="D1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="I1" t="s">
         <v>3</v>
@@ -655,10 +711,10 @@
         <v>6</v>
       </c>
       <c r="M1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -684,7 +740,7 @@
         <v>9</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I2" t="s">
         <v>9</v>
@@ -699,10 +755,10 @@
         <v>7</v>
       </c>
       <c r="M2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -743,10 +799,10 @@
         <v>19</v>
       </c>
       <c r="M3" t="s">
-        <v>43</v>
-      </c>
-      <c r="N3" t="s">
-        <v>46</v>
+        <v>42</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -889,7 +945,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -941,7 +997,7 @@
         <v>5</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -976,7 +1032,7 @@
         <v>5</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -1011,7 +1067,7 @@
         <v>5</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -1046,7 +1102,7 @@
         <v>5</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -1081,7 +1137,7 @@
         <v>5</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -1116,7 +1172,7 @@
         <v>5</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -1151,7 +1207,7 @@
         <v>5</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -1186,7 +1242,7 @@
         <v>5</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -1221,7 +1277,7 @@
         <v>5</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -1246,8 +1302,11 @@
       <c r="A18">
         <v>15</v>
       </c>
-      <c r="B18" t="s">
-        <v>55</v>
+      <c r="B18" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="E18">
         <v>50</v>
@@ -1262,7 +1321,7 @@
         <v>1</v>
       </c>
       <c r="I18">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -1277,7 +1336,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1285,26 +1344,26 @@
         <v>16</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E19">
         <v>50</v>
       </c>
       <c r="F19">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="G19">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H19">
         <v>1</v>
       </c>
       <c r="I19">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -1319,7 +1378,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1327,22 +1386,25 @@
         <v>17</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="E20">
         <v>50</v>
       </c>
       <c r="F20">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H20">
         <v>1</v>
       </c>
       <c r="I20">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -1362,7 +1424,10 @@
         <v>18</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>64</v>
+        <v>71</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="E21">
         <v>50</v>
@@ -1371,14 +1436,14 @@
         <v>50</v>
       </c>
       <c r="G21">
+        <v>40</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21">
         <v>20</v>
       </c>
-      <c r="H21">
-        <v>1</v>
-      </c>
-      <c r="I21">
-        <v>30</v>
-      </c>
       <c r="J21">
         <v>0</v>
       </c>
@@ -1386,7 +1451,7 @@
         <v>2</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M21">
         <v>0</v>
@@ -1404,10 +1469,10 @@
         <v>50</v>
       </c>
       <c r="F22">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -1433,25 +1498,25 @@
         <v>20</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E23">
         <v>50</v>
       </c>
       <c r="F23">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="G23">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H23">
         <v>1</v>
       </c>
       <c r="I23">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -1471,22 +1536,25 @@
         <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>40</v>
+        <v>75</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="E24">
         <v>50</v>
       </c>
       <c r="F24">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G24">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H24">
         <v>1</v>
       </c>
       <c r="I24">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -1501,7 +1569,7 @@
         <v>0</v>
       </c>
       <c r="N24" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1509,22 +1577,25 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>56</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>65</v>
       </c>
       <c r="E25">
         <v>50</v>
       </c>
       <c r="F25">
+        <v>50</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25">
         <v>10</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-      <c r="H25">
-        <v>1</v>
-      </c>
-      <c r="I25">
-        <v>2</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -1541,25 +1612,28 @@
     </row>
     <row r="26" spans="1:14">
       <c r="A26">
-        <v>1001</v>
+        <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>56</v>
+        <v>59</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="E26">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="F26">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="G26">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="H26">
         <v>1</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -1568,51 +1642,168 @@
         <v>2</v>
       </c>
       <c r="L26">
-        <v>10001</v>
+        <v>9</v>
       </c>
       <c r="M26">
         <v>0</v>
       </c>
-      <c r="N26" t="s">
-        <v>50</v>
+      <c r="N26" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E27">
+        <v>50</v>
+      </c>
+      <c r="F27">
+        <v>50</v>
+      </c>
+      <c r="G27">
+        <v>20</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27">
+        <v>15</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>2</v>
+      </c>
+      <c r="L27">
+        <v>10</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E28">
+        <v>50</v>
+      </c>
+      <c r="F28">
+        <v>50</v>
+      </c>
+      <c r="G28">
+        <v>20</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28">
+        <v>20</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>2</v>
+      </c>
+      <c r="L28">
+        <v>2</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29">
         <v>22</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B29" t="s">
+        <v>48</v>
+      </c>
+      <c r="E29">
+        <v>150</v>
+      </c>
+      <c r="F29">
+        <v>50</v>
+      </c>
+      <c r="G29">
+        <v>5</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="I29">
+        <v>2</v>
+      </c>
+      <c r="J29">
+        <v>1</v>
+      </c>
+      <c r="K29">
+        <v>2</v>
+      </c>
+      <c r="L29">
+        <v>3</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29" t="s">
         <v>49</v>
       </c>
-      <c r="E27">
-        <v>150</v>
-      </c>
-      <c r="F27">
-        <v>50</v>
-      </c>
-      <c r="G27">
-        <v>5</v>
-      </c>
-      <c r="H27">
-        <v>1</v>
-      </c>
-      <c r="I27">
-        <v>2</v>
-      </c>
-      <c r="J27">
-        <v>1</v>
-      </c>
-      <c r="K27">
-        <v>2</v>
-      </c>
-      <c r="L27">
-        <v>3</v>
-      </c>
-      <c r="M27">
-        <v>0</v>
-      </c>
-      <c r="N27" t="s">
-        <v>50</v>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30">
+        <v>1001</v>
+      </c>
+      <c r="B30" t="s">
+        <v>54</v>
+      </c>
+      <c r="E30">
+        <v>1000</v>
+      </c>
+      <c r="F30">
+        <v>1000</v>
+      </c>
+      <c r="G30">
+        <v>10</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>2</v>
+      </c>
+      <c r="L30">
+        <v>10001</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/Excels/Skill.xlsx
+++ b/Excels/Skill.xlsx
@@ -1,15 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyProject\WorldIsMine\Excels\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="19270" yWindow="-10" windowWidth="19160" windowHeight="10090"/>
+    <workbookView windowWidth="28800" windowHeight="11655"/>
   </bookViews>
   <sheets>
     <sheet name="SkillCfg" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="78">
   <si>
     <t>id</t>
   </si>
@@ -35,9 +40,24 @@
     <t>name</t>
   </si>
   <si>
+    <t>des</t>
+  </si>
+  <si>
+    <t>startEffect</t>
+  </si>
+  <si>
     <t>searchRange</t>
   </si>
   <si>
+    <t>atkRange</t>
+  </si>
+  <si>
+    <t>skillArea</t>
+  </si>
+  <si>
+    <t>skillDamageRate</t>
+  </si>
+  <si>
     <t>cd</t>
   </si>
   <si>
@@ -50,115 +70,26 @@
     <t>flyObjectId</t>
   </si>
   <si>
+    <t>buffId</t>
+  </si>
+  <si>
+    <t>dieType</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
     <t>string</t>
   </si>
   <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>#备注行</t>
-  </si>
-  <si>
-    <t>名字</t>
-  </si>
-  <si>
-    <t>索敌范围</t>
-  </si>
-  <si>
-    <t>攻击范围</t>
-  </si>
-  <si>
-    <t>伤害范围</t>
-  </si>
-  <si>
-    <t>伤害</t>
-  </si>
-  <si>
-    <t>冷却</t>
-  </si>
-  <si>
-    <t>是否是普工</t>
-  </si>
-  <si>
-    <t>1近战2远程</t>
-  </si>
-  <si>
-    <t>飞行物ID</t>
-  </si>
-  <si>
-    <t>刀盾近战</t>
-  </si>
-  <si>
-    <t>弓手远程</t>
-  </si>
-  <si>
-    <t>骑士攻击近战</t>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>施法特效</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>吕布普攻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>刘备普攻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>关羽普攻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>张飞普攻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>赵云普攻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>项羽普攻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>刘邦普攻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>韩信普攻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>樊哙普攻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>项庄普攻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰风暴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>天下无双</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>des</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>s</t>
     </r>
     <r>
@@ -166,172 +97,207 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>tring</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>int[]</t>
+  </si>
+  <si>
+    <t>#备注行</t>
+  </si>
+  <si>
+    <t>名字</t>
   </si>
   <si>
     <t>描述</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>buffId</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int[]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>施法特效</t>
+  </si>
+  <si>
+    <t>索敌范围</t>
+  </si>
+  <si>
+    <t>攻击长度</t>
+  </si>
+  <si>
+    <t>伤害范围</t>
+  </si>
+  <si>
+    <t>伤害</t>
+  </si>
+  <si>
+    <t>冷却</t>
+  </si>
+  <si>
+    <t>是否是普工</t>
+  </si>
+  <si>
+    <t>1近战2远程</t>
+  </si>
+  <si>
+    <t>飞行物ID</t>
   </si>
   <si>
     <t>buff信息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dieType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>死亡方式（）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刀盾近战</t>
+  </si>
+  <si>
+    <t>弓手远程</t>
+  </si>
+  <si>
+    <t>骑士攻击近战</t>
+  </si>
+  <si>
+    <t>枪</t>
+  </si>
+  <si>
+    <t>锤</t>
+  </si>
+  <si>
+    <t>投石</t>
+  </si>
+  <si>
+    <t>Explosion</t>
+  </si>
+  <si>
+    <t>吕布普攻</t>
+  </si>
+  <si>
+    <t>刘备普攻</t>
+  </si>
+  <si>
+    <t>关羽普攻</t>
+  </si>
+  <si>
+    <t>张飞普攻</t>
+  </si>
+  <si>
+    <t>赵云普攻</t>
+  </si>
+  <si>
+    <t>项羽普攻</t>
+  </si>
+  <si>
+    <t>刘邦普攻</t>
+  </si>
+  <si>
+    <t>韩信普攻</t>
+  </si>
+  <si>
+    <t>樊哙普攻</t>
+  </si>
+  <si>
+    <t>项庄普攻</t>
+  </si>
+  <si>
+    <t>雷霆万钧</t>
+  </si>
+  <si>
+    <t>乌云后雷电-远</t>
+  </si>
+  <si>
+    <t>燕人在此</t>
+  </si>
+  <si>
+    <t>Effects/熊吼土黄色</t>
+  </si>
+  <si>
+    <t>火龙追日</t>
+  </si>
+  <si>
+    <t>FX_火焰从天而降</t>
+  </si>
+  <si>
+    <t>裂地天刑</t>
+  </si>
+  <si>
+    <t>FX_剑落下爆炸</t>
+  </si>
+  <si>
+    <t>天下无双</t>
+  </si>
+  <si>
+    <t>倒转昆仑</t>
+  </si>
+  <si>
+    <t>Effects/FX_金色蓝色旋转体_周身技能</t>
+  </si>
+  <si>
+    <t>风卷残云</t>
+  </si>
+  <si>
+    <t>蓝色龙卷风</t>
   </si>
   <si>
     <t>Tornado</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bounce</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>投石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Explosion</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>atkRange</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>skillArea</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>skillDamageRate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>float</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奇门遁甲</t>
+  </si>
+  <si>
+    <t>飞剑</t>
+  </si>
+  <si>
+    <t>力劈华山</t>
+  </si>
+  <si>
+    <t>FX_从天而降的拳头土黄色</t>
+  </si>
+  <si>
+    <t>Squash</t>
+  </si>
+  <si>
+    <t>翻雷滚天</t>
+  </si>
+  <si>
+    <t>FX_红色飓风带雷电</t>
+  </si>
+  <si>
+    <t>万剑穿心</t>
+  </si>
+  <si>
+    <t>FX_冰箭从天而降爆炸</t>
   </si>
   <si>
     <t>全局技能-投石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>startEffect</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>奇门遁甲</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effects/熊吼土黄色</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effects/FX_金色蓝色旋转体_周身技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>力劈华山</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>乌云后雷电-远</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>火龙追日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FX_火焰从天而降</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FX_剑落下爆炸</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>蓝色龙卷风</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>飞剑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FX_从天而降的拳头土黄色</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>翻雷滚天</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FX_红色飓风带雷电</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>万剑穿心</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FX_冰箭从天而降爆炸</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>裂地天刑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>雷霆万钧</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>燕人在此</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>倒转昆仑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>风卷残云</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Squash</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全局技能-漫天剑雨-蓝</t>
+  </si>
+  <si>
+    <t>全局技能-漫天剑雨-红</t>
+  </si>
+  <si>
+    <t>全局技能-火龙吐息</t>
+  </si>
+  <si>
+    <t>Dissolve</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -340,30 +306,345 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="等线"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -371,25 +652,314 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -651,26 +1221,26 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:N34"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1"/>
-    <col min="2" max="3" width="18.08203125" customWidth="1"/>
-    <col min="4" max="4" width="45.6640625" customWidth="1"/>
-    <col min="5" max="6" width="19.4140625" customWidth="1"/>
-    <col min="7" max="7" width="20.58203125" customWidth="1"/>
-    <col min="8" max="8" width="32.83203125" customWidth="1"/>
-    <col min="9" max="9" width="29.83203125" customWidth="1"/>
-    <col min="10" max="10" width="24.58203125" customWidth="1"/>
-    <col min="11" max="11" width="31.33203125" customWidth="1"/>
-    <col min="12" max="12" width="12.33203125" customWidth="1"/>
-    <col min="14" max="14" width="28.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.2477876106195" customWidth="1"/>
+    <col min="2" max="3" width="18.0796460176991" customWidth="1"/>
+    <col min="4" max="4" width="45.6637168141593" customWidth="1"/>
+    <col min="5" max="6" width="19.4159292035398" customWidth="1"/>
+    <col min="7" max="7" width="20.5840707964602" customWidth="1"/>
+    <col min="8" max="8" width="32.8318584070796" customWidth="1"/>
+    <col min="9" max="9" width="29.8318584070796" customWidth="1"/>
+    <col min="10" max="10" width="24.5840707964602" customWidth="1"/>
+    <col min="11" max="11" width="31.3362831858407" customWidth="1"/>
+    <col min="12" max="12" width="12.3362831858407" customWidth="1"/>
+    <col min="14" max="14" width="28.6637168141593" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -681,128 +1251,128 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="N1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" ht="13.9" spans="1:14">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="I2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="L2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="M2" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="N2" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
         <v>24</v>
       </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
       <c r="G3" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I3" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J3" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="K3" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="L3" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="M3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -810,7 +1380,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="E4">
         <v>50</v>
@@ -825,7 +1395,7 @@
         <v>1</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -845,7 +1415,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="E5">
         <v>150</v>
@@ -860,7 +1430,7 @@
         <v>1</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -880,13 +1450,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E6">
         <v>50</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -895,7 +1465,7 @@
         <v>1</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -915,37 +1485,34 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E7">
         <v>50</v>
       </c>
       <c r="F7">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H7">
         <v>1</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7">
         <v>0</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -953,13 +1520,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="E8">
         <v>50</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -968,7 +1535,7 @@
         <v>1</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -985,45 +1552,48 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E9">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="F9">
+        <v>50</v>
+      </c>
+      <c r="G9">
         <v>5</v>
       </c>
-      <c r="G9">
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>5</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
         <v>2</v>
       </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9">
-        <v>2</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="K9">
-        <v>1</v>
-      </c>
       <c r="L9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M9">
         <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10">
-        <v>7</v>
+        <v>10001</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="E10">
         <v>50</v>
@@ -1032,13 +1602,13 @@
         <v>5</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H10">
         <v>1</v>
       </c>
       <c r="I10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1055,10 +1625,10 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11">
-        <v>8</v>
+        <v>10002</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="E11">
         <v>50</v>
@@ -1067,13 +1637,13 @@
         <v>5</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H11">
         <v>1</v>
       </c>
       <c r="I11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1090,10 +1660,10 @@
     </row>
     <row r="12" spans="1:14">
       <c r="A12">
-        <v>9</v>
+        <v>10003</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="E12">
         <v>50</v>
@@ -1102,13 +1672,13 @@
         <v>5</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H12">
         <v>1</v>
       </c>
       <c r="I12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1125,10 +1695,10 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13">
-        <v>10</v>
+        <v>10004</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="E13">
         <v>50</v>
@@ -1137,13 +1707,13 @@
         <v>5</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H13">
         <v>1</v>
       </c>
       <c r="I13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1160,10 +1730,10 @@
     </row>
     <row r="14" spans="1:14">
       <c r="A14">
-        <v>11</v>
+        <v>10005</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="E14">
         <v>50</v>
@@ -1172,13 +1742,13 @@
         <v>5</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H14">
         <v>1</v>
       </c>
       <c r="I14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1195,10 +1765,10 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15">
-        <v>12</v>
+        <v>10101</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E15">
         <v>50</v>
@@ -1207,13 +1777,13 @@
         <v>5</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H15">
         <v>1</v>
       </c>
       <c r="I15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1230,10 +1800,10 @@
     </row>
     <row r="16" spans="1:14">
       <c r="A16">
-        <v>13</v>
+        <v>10102</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E16">
         <v>50</v>
@@ -1242,13 +1812,13 @@
         <v>5</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H16">
         <v>1</v>
       </c>
       <c r="I16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -1265,10 +1835,10 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17">
-        <v>14</v>
+        <v>10103</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="E17">
         <v>50</v>
@@ -1277,13 +1847,13 @@
         <v>5</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H17">
         <v>1</v>
       </c>
       <c r="I17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -1300,73 +1870,63 @@
     </row>
     <row r="18" spans="1:14">
       <c r="A18">
-        <v>15</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>60</v>
+        <v>10104</v>
+      </c>
+      <c r="B18" t="s">
+        <v>48</v>
       </c>
       <c r="E18">
         <v>50</v>
       </c>
       <c r="F18">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="G18">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H18">
         <v>1</v>
       </c>
       <c r="I18">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L18">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M18">
         <v>0</v>
-      </c>
-      <c r="N18" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19">
-        <v>16</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1" t="s">
-        <v>57</v>
+        <v>10105</v>
+      </c>
+      <c r="B19" t="s">
+        <v>49</v>
       </c>
       <c r="E19">
         <v>50</v>
       </c>
       <c r="F19">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="G19">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="H19">
         <v>1</v>
       </c>
       <c r="I19">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19">
         <v>1</v>
@@ -1376,20 +1936,17 @@
       </c>
       <c r="M19">
         <v>0</v>
-      </c>
-      <c r="N19" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20">
-        <v>17</v>
+        <v>100001</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>62</v>
+        <v>50</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="E20">
         <v>50</v>
@@ -1398,7 +1955,7 @@
         <v>50</v>
       </c>
       <c r="G20">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -1413,7 +1970,7 @@
         <v>2</v>
       </c>
       <c r="L20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M20">
         <v>0</v>
@@ -1421,13 +1978,14 @@
     </row>
     <row r="21" spans="1:14">
       <c r="A21">
-        <v>18</v>
+        <v>100002</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>63</v>
+        <v>52</v>
+      </c>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="E21">
         <v>50</v>
@@ -1436,35 +1994,40 @@
         <v>50</v>
       </c>
       <c r="G21">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H21">
         <v>1</v>
       </c>
       <c r="I21">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L21">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M21">
         <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22">
-        <v>19</v>
+        <v>100003</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C22" s="1"/>
+        <v>54</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E22">
         <v>50</v>
       </c>
@@ -1472,22 +2035,22 @@
         <v>50</v>
       </c>
       <c r="G22">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="H22">
         <v>1</v>
       </c>
       <c r="I22">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
       <c r="K22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M22">
         <v>0</v>
@@ -1495,37 +2058,37 @@
     </row>
     <row r="23" spans="1:14">
       <c r="A23">
+        <v>100004</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E23">
+        <v>50</v>
+      </c>
+      <c r="F23">
+        <v>50</v>
+      </c>
+      <c r="G23">
+        <v>10</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
         <v>20</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E23">
-        <v>50</v>
-      </c>
-      <c r="F23">
-        <v>50</v>
-      </c>
-      <c r="G23">
-        <v>50</v>
-      </c>
-      <c r="H23">
-        <v>1</v>
-      </c>
-      <c r="I23">
-        <v>10</v>
-      </c>
       <c r="J23">
         <v>0</v>
       </c>
       <c r="K23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M23">
         <v>0</v>
@@ -1533,14 +2096,12 @@
     </row>
     <row r="24" spans="1:14">
       <c r="A24">
-        <v>21</v>
+        <v>100005</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>64</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="C24" s="1"/>
       <c r="E24">
         <v>50</v>
       </c>
@@ -1548,39 +2109,36 @@
         <v>50</v>
       </c>
       <c r="G24">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H24">
         <v>1</v>
       </c>
       <c r="I24">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L24">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M24">
         <v>0</v>
-      </c>
-      <c r="N24" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25">
-        <v>23</v>
-      </c>
-      <c r="B25" t="s">
-        <v>56</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>65</v>
+        <v>100006</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="E25">
         <v>50</v>
@@ -1589,7 +2147,7 @@
         <v>50</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -1601,10 +2159,10 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L25">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M25">
         <v>0</v>
@@ -1612,13 +2170,13 @@
     </row>
     <row r="26" spans="1:14">
       <c r="A26">
-        <v>24</v>
-      </c>
-      <c r="B26" t="s">
-        <v>59</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>66</v>
+        <v>100007</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="E26">
         <v>50</v>
@@ -1627,13 +2185,13 @@
         <v>50</v>
       </c>
       <c r="G26">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="H26">
         <v>1</v>
       </c>
       <c r="I26">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -1642,24 +2200,24 @@
         <v>2</v>
       </c>
       <c r="L26">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M26">
         <v>0</v>
       </c>
-      <c r="N26" s="1" t="s">
-        <v>76</v>
+      <c r="N26" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27">
-        <v>25</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>68</v>
+        <v>100008</v>
+      </c>
+      <c r="B27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>65</v>
       </c>
       <c r="E27">
         <v>50</v>
@@ -1668,13 +2226,13 @@
         <v>50</v>
       </c>
       <c r="G27">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H27">
         <v>1</v>
       </c>
       <c r="I27">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -1683,24 +2241,21 @@
         <v>2</v>
       </c>
       <c r="L27">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M27">
         <v>0</v>
-      </c>
-      <c r="N27" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28">
-        <v>26</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>70</v>
+        <v>100009</v>
+      </c>
+      <c r="B28" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="E28">
         <v>50</v>
@@ -1709,7 +2264,7 @@
         <v>50</v>
       </c>
       <c r="G28">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -1724,62 +2279,71 @@
         <v>2</v>
       </c>
       <c r="L28">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M28">
         <v>0</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29">
-        <v>22</v>
-      </c>
-      <c r="B29" t="s">
-        <v>48</v>
+        <v>100010</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="E29">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F29">
         <v>50</v>
       </c>
       <c r="G29">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H29">
         <v>1</v>
       </c>
       <c r="I29">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="J29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29">
         <v>2</v>
       </c>
       <c r="L29">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M29">
         <v>0</v>
       </c>
       <c r="N29" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30">
-        <v>1001</v>
-      </c>
-      <c r="B30" t="s">
-        <v>54</v>
+        <v>100011</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>72</v>
       </c>
       <c r="E30">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="F30">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="G30">
         <v>10</v>
@@ -1788,7 +2352,7 @@
         <v>1</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -1797,18 +2361,161 @@
         <v>2</v>
       </c>
       <c r="L30">
-        <v>10001</v>
+        <v>2</v>
       </c>
       <c r="M30">
         <v>0</v>
       </c>
-      <c r="N30" t="s">
-        <v>49</v>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31">
+        <v>1001</v>
+      </c>
+      <c r="B31" t="s">
+        <v>73</v>
+      </c>
+      <c r="E31">
+        <v>1000</v>
+      </c>
+      <c r="F31">
+        <v>1000</v>
+      </c>
+      <c r="G31">
+        <v>10</v>
+      </c>
+      <c r="H31">
+        <v>100</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>2</v>
+      </c>
+      <c r="L31">
+        <v>1001</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32">
+        <v>1002</v>
+      </c>
+      <c r="B32" t="s">
+        <v>74</v>
+      </c>
+      <c r="E32">
+        <v>1000</v>
+      </c>
+      <c r="F32">
+        <v>1000</v>
+      </c>
+      <c r="G32">
+        <v>2</v>
+      </c>
+      <c r="H32">
+        <v>100</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>2</v>
+      </c>
+      <c r="L32">
+        <v>1002</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" customFormat="1" spans="1:14">
+      <c r="A33">
+        <v>1003</v>
+      </c>
+      <c r="B33" t="s">
+        <v>75</v>
+      </c>
+      <c r="E33">
+        <v>1000</v>
+      </c>
+      <c r="F33">
+        <v>1000</v>
+      </c>
+      <c r="G33">
+        <v>2</v>
+      </c>
+      <c r="H33">
+        <v>100</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>2</v>
+      </c>
+      <c r="L33">
+        <v>1003</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34">
+        <v>1004</v>
+      </c>
+      <c r="B34" t="s">
+        <v>76</v>
+      </c>
+      <c r="E34">
+        <v>1000</v>
+      </c>
+      <c r="F34">
+        <v>1000</v>
+      </c>
+      <c r="G34">
+        <v>2</v>
+      </c>
+      <c r="H34">
+        <v>1000</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>2</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Excels/Skill.xlsx
+++ b/Excels/Skill.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11655"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="SkillCfg" sheetId="1" r:id="rId1"/>
@@ -1383,10 +1383,10 @@
         <v>33</v>
       </c>
       <c r="E4">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1418,7 +1418,7 @@
         <v>34</v>
       </c>
       <c r="E5">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="F5">
         <v>50</v>
@@ -1453,7 +1453,7 @@
         <v>35</v>
       </c>
       <c r="E6">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="F6">
         <v>6</v>
@@ -1488,10 +1488,10 @@
         <v>36</v>
       </c>
       <c r="E7">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1523,10 +1523,10 @@
         <v>37</v>
       </c>
       <c r="E8">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1558,7 +1558,7 @@
         <v>38</v>
       </c>
       <c r="E9">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="F9">
         <v>50</v>
@@ -1596,7 +1596,7 @@
         <v>40</v>
       </c>
       <c r="E10">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -1631,7 +1631,7 @@
         <v>41</v>
       </c>
       <c r="E11">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -1666,7 +1666,7 @@
         <v>42</v>
       </c>
       <c r="E12">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -1701,7 +1701,7 @@
         <v>43</v>
       </c>
       <c r="E13">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -1736,7 +1736,7 @@
         <v>44</v>
       </c>
       <c r="E14">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -1771,7 +1771,7 @@
         <v>45</v>
       </c>
       <c r="E15">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -1806,7 +1806,7 @@
         <v>46</v>
       </c>
       <c r="E16">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -1841,7 +1841,7 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -1876,7 +1876,7 @@
         <v>48</v>
       </c>
       <c r="E18">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -1911,7 +1911,7 @@
         <v>49</v>
       </c>
       <c r="E19">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -1949,7 +1949,7 @@
         <v>51</v>
       </c>
       <c r="E20">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="F20">
         <v>50</v>
@@ -1988,7 +1988,7 @@
         <v>53</v>
       </c>
       <c r="E21">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="F21">
         <v>50</v>
@@ -2029,7 +2029,7 @@
         <v>55</v>
       </c>
       <c r="E22">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="F22">
         <v>50</v>
@@ -2067,7 +2067,7 @@
         <v>57</v>
       </c>
       <c r="E23">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="F23">
         <v>50</v>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="C24" s="1"/>
       <c r="E24">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="F24">
         <v>50</v>
@@ -2141,7 +2141,7 @@
         <v>60</v>
       </c>
       <c r="E25">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="F25">
         <v>50</v>
@@ -2179,7 +2179,7 @@
         <v>62</v>
       </c>
       <c r="E26">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="F26">
         <v>50</v>
@@ -2220,7 +2220,7 @@
         <v>65</v>
       </c>
       <c r="E27">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="F27">
         <v>50</v>
@@ -2258,7 +2258,7 @@
         <v>67</v>
       </c>
       <c r="E28">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="F28">
         <v>50</v>
@@ -2299,7 +2299,7 @@
         <v>70</v>
       </c>
       <c r="E29">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="F29">
         <v>50</v>
@@ -2340,7 +2340,7 @@
         <v>72</v>
       </c>
       <c r="E30">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="F30">
         <v>50</v>

--- a/Excels/Skill.xlsx
+++ b/Excels/Skill.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="110">
   <si>
     <t>id</t>
   </si>
@@ -155,6 +155,9 @@
     <t>刀盾近战</t>
   </si>
   <si>
+    <t>Dissolve</t>
+  </si>
+  <si>
     <t>弓手远程</t>
   </si>
   <si>
@@ -188,6 +191,21 @@
     <t>赵云普攻</t>
   </si>
   <si>
+    <t>马超</t>
+  </si>
+  <si>
+    <t>黄忠</t>
+  </si>
+  <si>
+    <t>诸葛亮</t>
+  </si>
+  <si>
+    <t>夏侯惇</t>
+  </si>
+  <si>
+    <t>曹操</t>
+  </si>
+  <si>
     <t>项羽普攻</t>
   </si>
   <si>
@@ -203,6 +221,21 @@
     <t>项庄普攻</t>
   </si>
   <si>
+    <t>孙膑</t>
+  </si>
+  <si>
+    <t>廉颇</t>
+  </si>
+  <si>
+    <t>卫青</t>
+  </si>
+  <si>
+    <t>霍去病</t>
+  </si>
+  <si>
+    <t>李广</t>
+  </si>
+  <si>
     <t>雷霆万钧</t>
   </si>
   <si>
@@ -230,6 +263,9 @@
     <t>天下无双</t>
   </si>
   <si>
+    <t>攻速加，攻击加</t>
+  </si>
+  <si>
     <t>倒转昆仑</t>
   </si>
   <si>
@@ -272,6 +308,69 @@
     <t>FX_冰箭从天而降爆炸</t>
   </si>
   <si>
+    <t>换位置</t>
+  </si>
+  <si>
+    <t>移形换位</t>
+  </si>
+  <si>
+    <t>把士兵传送至出生点</t>
+  </si>
+  <si>
+    <t>天降神兵</t>
+  </si>
+  <si>
+    <t>援军从侧面入场</t>
+  </si>
+  <si>
+    <t>金刚不败</t>
+  </si>
+  <si>
+    <t>最后一点血不死</t>
+  </si>
+  <si>
+    <t>气灼八荒</t>
+  </si>
+  <si>
+    <t>周身伤害</t>
+  </si>
+  <si>
+    <t>吞纳万象</t>
+  </si>
+  <si>
+    <t>吸力</t>
+  </si>
+  <si>
+    <t>截驰断道</t>
+  </si>
+  <si>
+    <t>阻断的墙壁</t>
+  </si>
+  <si>
+    <t>矢贯长阵</t>
+  </si>
+  <si>
+    <t>穿透一击</t>
+  </si>
+  <si>
+    <t>涅槃</t>
+  </si>
+  <si>
+    <t>重生</t>
+  </si>
+  <si>
+    <t>淘汰之刃</t>
+  </si>
+  <si>
+    <t>复制</t>
+  </si>
+  <si>
+    <t>生命汲取</t>
+  </si>
+  <si>
+    <t>逆伤</t>
+  </si>
+  <si>
     <t>全局技能-投石</t>
   </si>
   <si>
@@ -281,10 +380,7 @@
     <t>全局技能-漫天剑雨-红</t>
   </si>
   <si>
-    <t>全局技能-火龙吐息</t>
-  </si>
-  <si>
-    <t>Dissolve</t>
+    <t>全局技能-火烧连营</t>
   </si>
 </sst>
 </file>
@@ -1227,11 +1323,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:N57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85"/>
   <cols>
     <col min="1" max="1" width="15.2477876106195" customWidth="1"/>
-    <col min="2" max="3" width="18.0796460176991" customWidth="1"/>
+    <col min="2" max="3" width="23.787610619469" customWidth="1"/>
     <col min="4" max="4" width="45.6637168141593" customWidth="1"/>
     <col min="5" max="6" width="19.4159292035398" customWidth="1"/>
     <col min="7" max="7" width="20.5840707964602" customWidth="1"/>
@@ -1409,13 +1505,16 @@
       <c r="M4">
         <v>0</v>
       </c>
+      <c r="N4" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5">
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E5">
         <v>120</v>
@@ -1450,7 +1549,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E6">
         <v>120</v>
@@ -1485,7 +1584,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E7">
         <v>120</v>
@@ -1520,7 +1619,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E8">
         <v>120</v>
@@ -1555,7 +1654,7 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E9">
         <v>120</v>
@@ -1585,7 +1684,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1593,7 +1692,7 @@
         <v>10001</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E10">
         <v>120</v>
@@ -1628,7 +1727,7 @@
         <v>10002</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E11">
         <v>120</v>
@@ -1663,7 +1762,7 @@
         <v>10003</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E12">
         <v>120</v>
@@ -1698,7 +1797,7 @@
         <v>10004</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E13">
         <v>120</v>
@@ -1733,7 +1832,7 @@
         <v>10005</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E14">
         <v>120</v>
@@ -1763,12 +1862,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" customFormat="1" spans="1:14">
       <c r="A15">
-        <v>10101</v>
+        <v>10006</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E15">
         <v>120</v>
@@ -1798,12 +1897,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" customFormat="1" spans="1:14">
       <c r="A16">
-        <v>10102</v>
+        <v>10007</v>
       </c>
       <c r="B16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E16">
         <v>120</v>
@@ -1833,12 +1932,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" customFormat="1" spans="1:14">
       <c r="A17">
-        <v>10103</v>
+        <v>10008</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E17">
         <v>120</v>
@@ -1868,12 +1967,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" customFormat="1" spans="1:14">
       <c r="A18">
-        <v>10104</v>
+        <v>10009</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E18">
         <v>120</v>
@@ -1903,12 +2002,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" customFormat="1" spans="1:14">
       <c r="A19">
-        <v>10105</v>
+        <v>10010</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E19">
         <v>120</v>
@@ -1940,37 +2039,34 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20">
-        <v>100001</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C20" s="1" t="s">
+        <v>10101</v>
+      </c>
+      <c r="B20" t="s">
         <v>51</v>
       </c>
       <c r="E20">
         <v>120</v>
       </c>
       <c r="F20">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="G20">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H20">
         <v>1</v>
       </c>
       <c r="I20">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M20">
         <v>0</v>
@@ -1978,32 +2074,28 @@
     </row>
     <row r="21" spans="1:14">
       <c r="A21">
-        <v>100002</v>
-      </c>
-      <c r="B21" s="1" t="s">
+        <v>10102</v>
+      </c>
+      <c r="B21" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="E21">
         <v>120</v>
       </c>
       <c r="F21">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="G21">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H21">
         <v>1</v>
       </c>
       <c r="I21">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21">
         <v>1</v>
@@ -2013,44 +2105,38 @@
       </c>
       <c r="M21">
         <v>0</v>
-      </c>
-      <c r="N21" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22">
-        <v>100003</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>55</v>
+        <v>10103</v>
+      </c>
+      <c r="B22" t="s">
+        <v>53</v>
       </c>
       <c r="E22">
         <v>120</v>
       </c>
       <c r="F22">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="G22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H22">
         <v>1</v>
       </c>
       <c r="I22">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L22">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M22">
         <v>0</v>
@@ -2058,37 +2144,34 @@
     </row>
     <row r="23" spans="1:14">
       <c r="A23">
-        <v>100004</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>57</v>
+        <v>10104</v>
+      </c>
+      <c r="B23" t="s">
+        <v>54</v>
       </c>
       <c r="E23">
         <v>120</v>
       </c>
       <c r="F23">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="G23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H23">
         <v>1</v>
       </c>
       <c r="I23">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L23">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M23">
         <v>0</v>
@@ -2096,29 +2179,28 @@
     </row>
     <row r="24" spans="1:14">
       <c r="A24">
-        <v>100005</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C24" s="1"/>
+        <v>10105</v>
+      </c>
+      <c r="B24" t="s">
+        <v>55</v>
+      </c>
       <c r="E24">
         <v>120</v>
       </c>
       <c r="F24">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="G24">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="H24">
         <v>1</v>
       </c>
       <c r="I24">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24">
         <v>1</v>
@@ -2132,31 +2214,28 @@
     </row>
     <row r="25" spans="1:14">
       <c r="A25">
-        <v>100006</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>60</v>
+        <v>10106</v>
+      </c>
+      <c r="B25" t="s">
+        <v>56</v>
       </c>
       <c r="E25">
         <v>120</v>
       </c>
       <c r="F25">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="G25">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H25">
         <v>1</v>
       </c>
       <c r="I25">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25">
         <v>1</v>
@@ -2170,78 +2249,69 @@
     </row>
     <row r="26" spans="1:14">
       <c r="A26">
-        <v>100007</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>62</v>
+        <v>10107</v>
+      </c>
+      <c r="B26" t="s">
+        <v>57</v>
       </c>
       <c r="E26">
         <v>120</v>
       </c>
       <c r="F26">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="G26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H26">
         <v>1</v>
       </c>
       <c r="I26">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L26">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M26">
         <v>0</v>
-      </c>
-      <c r="N26" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27">
-        <v>100008</v>
+        <v>10108</v>
       </c>
       <c r="B27" t="s">
-        <v>64</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="E27">
         <v>120</v>
       </c>
       <c r="F27">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H27">
         <v>1</v>
       </c>
       <c r="I27">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L27">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M27">
         <v>0</v>
@@ -2249,95 +2319,83 @@
     </row>
     <row r="28" spans="1:14">
       <c r="A28">
-        <v>100009</v>
+        <v>10109</v>
       </c>
       <c r="B28" t="s">
-        <v>66</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="E28">
         <v>120</v>
       </c>
       <c r="F28">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="G28">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H28">
         <v>1</v>
       </c>
       <c r="I28">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L28">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M28">
         <v>0</v>
-      </c>
-      <c r="N28" s="1" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29">
-        <v>100010</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>70</v>
+        <v>10110</v>
+      </c>
+      <c r="B29" t="s">
+        <v>60</v>
       </c>
       <c r="E29">
         <v>120</v>
       </c>
       <c r="F29">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="G29">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H29">
         <v>1</v>
       </c>
       <c r="I29">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L29">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M29">
         <v>0</v>
-      </c>
-      <c r="N29" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30">
-        <v>100011</v>
+        <v>100001</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>72</v>
+        <v>61</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="E30">
         <v>120</v>
@@ -2361,7 +2419,7 @@
         <v>2</v>
       </c>
       <c r="L30">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M30">
         <v>0</v>
@@ -2369,63 +2427,70 @@
     </row>
     <row r="31" spans="1:14">
       <c r="A31">
-        <v>1001</v>
-      </c>
-      <c r="B31" t="s">
-        <v>73</v>
+        <v>100002</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="E31">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="F31">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="G31">
+        <v>15</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="I31">
         <v>10</v>
       </c>
-      <c r="H31">
-        <v>100</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
       <c r="J31">
         <v>0</v>
       </c>
       <c r="K31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L31">
-        <v>1001</v>
+        <v>0</v>
       </c>
       <c r="M31">
         <v>0</v>
       </c>
       <c r="N31" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32">
-        <v>1002</v>
-      </c>
-      <c r="B32" t="s">
-        <v>74</v>
+        <v>100003</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="E32">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="F32">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H32">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -2434,33 +2499,36 @@
         <v>2</v>
       </c>
       <c r="L32">
-        <v>1002</v>
+        <v>7</v>
       </c>
       <c r="M32">
         <v>0</v>
       </c>
     </row>
-    <row r="33" customFormat="1" spans="1:14">
+    <row r="33" spans="1:14">
       <c r="A33">
-        <v>1003</v>
-      </c>
-      <c r="B33" t="s">
-        <v>75</v>
+        <v>100004</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="E33">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="F33">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="G33">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H33">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -2469,7 +2537,7 @@
         <v>2</v>
       </c>
       <c r="L33">
-        <v>1003</v>
+        <v>8</v>
       </c>
       <c r="M33">
         <v>0</v>
@@ -2477,40 +2545,917 @@
     </row>
     <row r="34" spans="1:14">
       <c r="A34">
+        <v>100005</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E34">
+        <v>120</v>
+      </c>
+      <c r="F34">
+        <v>50</v>
+      </c>
+      <c r="G34">
+        <v>50</v>
+      </c>
+      <c r="H34">
+        <v>1</v>
+      </c>
+      <c r="I34">
+        <v>30</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>1</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35">
+        <v>100006</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E35">
+        <v>120</v>
+      </c>
+      <c r="F35">
+        <v>50</v>
+      </c>
+      <c r="G35">
+        <v>15</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35">
+        <v>10</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>1</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36">
+        <v>100007</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E36">
+        <v>120</v>
+      </c>
+      <c r="F36">
+        <v>50</v>
+      </c>
+      <c r="G36">
+        <v>10</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36">
+        <v>15</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>2</v>
+      </c>
+      <c r="L36">
+        <v>4</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37">
+        <v>100008</v>
+      </c>
+      <c r="B37" t="s">
+        <v>76</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E37">
+        <v>120</v>
+      </c>
+      <c r="F37">
+        <v>50</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>1</v>
+      </c>
+      <c r="I37">
+        <v>10</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>2</v>
+      </c>
+      <c r="L37">
+        <v>5</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38">
+        <v>100009</v>
+      </c>
+      <c r="B38" t="s">
+        <v>78</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E38">
+        <v>120</v>
+      </c>
+      <c r="F38">
+        <v>50</v>
+      </c>
+      <c r="G38">
+        <v>15</v>
+      </c>
+      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="I38">
+        <v>20</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>2</v>
+      </c>
+      <c r="L38">
+        <v>9</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39">
+        <v>100010</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E39">
+        <v>120</v>
+      </c>
+      <c r="F39">
+        <v>50</v>
+      </c>
+      <c r="G39">
+        <v>10</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+      <c r="I39">
+        <v>15</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>2</v>
+      </c>
+      <c r="L39">
+        <v>10</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40">
+        <v>100011</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E40">
+        <v>120</v>
+      </c>
+      <c r="F40">
+        <v>50</v>
+      </c>
+      <c r="G40">
+        <v>10</v>
+      </c>
+      <c r="H40">
+        <v>1</v>
+      </c>
+      <c r="I40">
+        <v>20</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>2</v>
+      </c>
+      <c r="L40">
+        <v>2</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" customFormat="1" spans="1:14">
+      <c r="A41">
+        <v>100012</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E41">
+        <v>120</v>
+      </c>
+      <c r="F41">
+        <v>50</v>
+      </c>
+      <c r="G41">
+        <v>10</v>
+      </c>
+      <c r="H41">
+        <v>1</v>
+      </c>
+      <c r="I41">
+        <v>20</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>2</v>
+      </c>
+      <c r="L41">
+        <v>2</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" customFormat="1" spans="1:14">
+      <c r="A42">
+        <v>100013</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E42">
+        <v>120</v>
+      </c>
+      <c r="F42">
+        <v>50</v>
+      </c>
+      <c r="G42">
+        <v>10</v>
+      </c>
+      <c r="H42">
+        <v>1</v>
+      </c>
+      <c r="I42">
+        <v>20</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>2</v>
+      </c>
+      <c r="L42">
+        <v>2</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" customFormat="1" spans="1:14">
+      <c r="A43">
+        <v>100014</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E43">
+        <v>120</v>
+      </c>
+      <c r="F43">
+        <v>50</v>
+      </c>
+      <c r="G43">
+        <v>10</v>
+      </c>
+      <c r="H43">
+        <v>1</v>
+      </c>
+      <c r="I43">
+        <v>20</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>2</v>
+      </c>
+      <c r="L43">
+        <v>2</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" customFormat="1" spans="1:14">
+      <c r="A44">
+        <v>100015</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E44">
+        <v>120</v>
+      </c>
+      <c r="F44">
+        <v>50</v>
+      </c>
+      <c r="G44">
+        <v>10</v>
+      </c>
+      <c r="H44">
+        <v>1</v>
+      </c>
+      <c r="I44">
+        <v>20</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>2</v>
+      </c>
+      <c r="L44">
+        <v>2</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" customFormat="1" spans="1:14">
+      <c r="A45">
+        <v>100016</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E45">
+        <v>120</v>
+      </c>
+      <c r="F45">
+        <v>50</v>
+      </c>
+      <c r="G45">
+        <v>10</v>
+      </c>
+      <c r="H45">
+        <v>1</v>
+      </c>
+      <c r="I45">
+        <v>20</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>2</v>
+      </c>
+      <c r="L45">
+        <v>2</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" customFormat="1" spans="1:14">
+      <c r="A46">
+        <v>100017</v>
+      </c>
+      <c r="B46" t="s">
+        <v>94</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E46">
+        <v>120</v>
+      </c>
+      <c r="F46">
+        <v>50</v>
+      </c>
+      <c r="G46">
+        <v>10</v>
+      </c>
+      <c r="H46">
+        <v>1</v>
+      </c>
+      <c r="I46">
+        <v>20</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>2</v>
+      </c>
+      <c r="L46">
+        <v>2</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" customFormat="1" spans="1:14">
+      <c r="A47">
+        <v>100018</v>
+      </c>
+      <c r="B47" t="s">
+        <v>96</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E47">
+        <v>120</v>
+      </c>
+      <c r="F47">
+        <v>50</v>
+      </c>
+      <c r="G47">
+        <v>10</v>
+      </c>
+      <c r="H47">
+        <v>1</v>
+      </c>
+      <c r="I47">
+        <v>20</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>2</v>
+      </c>
+      <c r="L47">
+        <v>2</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" spans="1:14">
+      <c r="A48">
+        <v>100019</v>
+      </c>
+      <c r="B48" t="s">
+        <v>98</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E48">
+        <v>120</v>
+      </c>
+      <c r="F48">
+        <v>50</v>
+      </c>
+      <c r="G48">
+        <v>10</v>
+      </c>
+      <c r="H48">
+        <v>1</v>
+      </c>
+      <c r="I48">
+        <v>20</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>2</v>
+      </c>
+      <c r="L48">
+        <v>2</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" customFormat="1" spans="1:14">
+      <c r="A49">
+        <v>100020</v>
+      </c>
+      <c r="B49" t="s">
+        <v>100</v>
+      </c>
+      <c r="C49" t="s">
+        <v>101</v>
+      </c>
+      <c r="E49">
+        <v>120</v>
+      </c>
+      <c r="F49">
+        <v>50</v>
+      </c>
+      <c r="G49">
+        <v>10</v>
+      </c>
+      <c r="H49">
+        <v>1</v>
+      </c>
+      <c r="I49">
+        <v>20</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>2</v>
+      </c>
+      <c r="L49">
+        <v>2</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" customFormat="1" spans="1:14">
+      <c r="A50">
+        <v>100021</v>
+      </c>
+      <c r="B50" t="s">
+        <v>102</v>
+      </c>
+      <c r="C50" t="s">
+        <v>102</v>
+      </c>
+      <c r="E50">
+        <v>120</v>
+      </c>
+      <c r="F50">
+        <v>50</v>
+      </c>
+      <c r="G50">
+        <v>10</v>
+      </c>
+      <c r="H50">
+        <v>1</v>
+      </c>
+      <c r="I50">
+        <v>20</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>2</v>
+      </c>
+      <c r="L50">
+        <v>2</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" customFormat="1" spans="1:14">
+      <c r="A51">
+        <v>100022</v>
+      </c>
+      <c r="B51" t="s">
+        <v>103</v>
+      </c>
+      <c r="C51" t="s">
+        <v>103</v>
+      </c>
+      <c r="E51">
+        <v>120</v>
+      </c>
+      <c r="F51">
+        <v>50</v>
+      </c>
+      <c r="G51">
+        <v>10</v>
+      </c>
+      <c r="H51">
+        <v>1</v>
+      </c>
+      <c r="I51">
+        <v>20</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>2</v>
+      </c>
+      <c r="L51">
+        <v>2</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" customFormat="1" spans="1:14">
+      <c r="A52">
+        <v>100023</v>
+      </c>
+      <c r="B52" t="s">
+        <v>104</v>
+      </c>
+      <c r="C52" t="s">
+        <v>103</v>
+      </c>
+      <c r="E52">
+        <v>120</v>
+      </c>
+      <c r="F52">
+        <v>50</v>
+      </c>
+      <c r="G52">
+        <v>10</v>
+      </c>
+      <c r="H52">
+        <v>1</v>
+      </c>
+      <c r="I52">
+        <v>20</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>2</v>
+      </c>
+      <c r="L52">
+        <v>2</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" customFormat="1" spans="1:14">
+      <c r="A53">
+        <v>100024</v>
+      </c>
+      <c r="B53" t="s">
+        <v>105</v>
+      </c>
+      <c r="C53" t="s">
+        <v>105</v>
+      </c>
+      <c r="E53">
+        <v>120</v>
+      </c>
+      <c r="F53">
+        <v>50</v>
+      </c>
+      <c r="G53">
+        <v>10</v>
+      </c>
+      <c r="H53">
+        <v>1</v>
+      </c>
+      <c r="I53">
+        <v>20</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>2</v>
+      </c>
+      <c r="L53">
+        <v>2</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
+      <c r="A54">
+        <v>1001</v>
+      </c>
+      <c r="B54" t="s">
+        <v>106</v>
+      </c>
+      <c r="E54">
+        <v>1000</v>
+      </c>
+      <c r="F54">
+        <v>1000</v>
+      </c>
+      <c r="G54">
+        <v>10</v>
+      </c>
+      <c r="H54">
+        <v>100</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>2</v>
+      </c>
+      <c r="L54">
+        <v>1001</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14">
+      <c r="A55">
+        <v>1002</v>
+      </c>
+      <c r="B55" t="s">
+        <v>107</v>
+      </c>
+      <c r="E55">
+        <v>1000</v>
+      </c>
+      <c r="F55">
+        <v>1000</v>
+      </c>
+      <c r="G55">
+        <v>2</v>
+      </c>
+      <c r="H55">
+        <v>100</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>2</v>
+      </c>
+      <c r="L55">
+        <v>1002</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" customFormat="1" spans="1:14">
+      <c r="A56">
+        <v>1003</v>
+      </c>
+      <c r="B56" t="s">
+        <v>108</v>
+      </c>
+      <c r="E56">
+        <v>1000</v>
+      </c>
+      <c r="F56">
+        <v>1000</v>
+      </c>
+      <c r="G56">
+        <v>2</v>
+      </c>
+      <c r="H56">
+        <v>100</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>2</v>
+      </c>
+      <c r="L56">
+        <v>1003</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14">
+      <c r="A57">
         <v>1004</v>
       </c>
-      <c r="B34" t="s">
-        <v>76</v>
-      </c>
-      <c r="E34">
+      <c r="B57" t="s">
+        <v>109</v>
+      </c>
+      <c r="E57">
         <v>1000</v>
       </c>
-      <c r="F34">
+      <c r="F57">
         <v>1000</v>
       </c>
-      <c r="G34">
-        <v>2</v>
-      </c>
-      <c r="H34">
+      <c r="G57">
+        <v>2</v>
+      </c>
+      <c r="H57">
         <v>1000</v>
       </c>
-      <c r="I34">
-        <v>0</v>
-      </c>
-      <c r="J34">
-        <v>0</v>
-      </c>
-      <c r="K34">
-        <v>2</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
-      <c r="N34" t="s">
-        <v>77</v>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>2</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/Excels/Skill.xlsx
+++ b/Excels/Skill.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="SkillCfg" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="122">
   <si>
     <t>id</t>
   </si>
@@ -64,6 +64,9 @@
     <t>normal</t>
   </si>
   <si>
+    <t>needTarget</t>
+  </si>
+  <si>
     <t>skillType</t>
   </si>
   <si>
@@ -74,6 +77,9 @@
   </si>
   <si>
     <t>dieType</t>
+  </si>
+  <si>
+    <t>skillParam</t>
   </si>
   <si>
     <t>int</t>
@@ -140,7 +146,10 @@
     <t>是否是普工</t>
   </si>
   <si>
-    <t>1近战2远程</t>
+    <t>0表示不需要，1表示需要 2.目标自己3一定是英雄</t>
+  </si>
+  <si>
+    <t>(remote,normalClose,callFriend,transformToCityDoor,triggerBeforeDie,killNow,push,createWall)</t>
   </si>
   <si>
     <t>飞行物ID</t>
@@ -152,15 +161,24 @@
     <t>死亡方式（）</t>
   </si>
   <si>
+    <t>技能参数</t>
+  </si>
+  <si>
     <t>刀盾近战</t>
   </si>
   <si>
+    <t>normalClose</t>
+  </si>
+  <si>
     <t>Dissolve</t>
   </si>
   <si>
     <t>弓手远程</t>
   </si>
   <si>
+    <t>remote</t>
+  </si>
+  <si>
     <t>骑士攻击近战</t>
   </si>
   <si>
@@ -293,9 +311,6 @@
     <t>FX_从天而降的拳头土黄色</t>
   </si>
   <si>
-    <t>Squash</t>
-  </si>
-  <si>
     <t>翻雷滚天</t>
   </si>
   <si>
@@ -317,18 +332,27 @@
     <t>把士兵传送至出生点</t>
   </si>
   <si>
+    <t>transformToCityDoor</t>
+  </si>
+  <si>
     <t>天降神兵</t>
   </si>
   <si>
     <t>援军从侧面入场</t>
   </si>
   <si>
+    <t>callFriend</t>
+  </si>
+  <si>
     <t>金刚不败</t>
   </si>
   <si>
     <t>最后一点血不死</t>
   </si>
   <si>
+    <t>triggerBeforeDie</t>
+  </si>
+  <si>
     <t>气灼八荒</t>
   </si>
   <si>
@@ -347,13 +371,19 @@
     <t>阻断的墙壁</t>
   </si>
   <si>
+    <t>createWall</t>
+  </si>
+  <si>
+    <t>10,5,5</t>
+  </si>
+  <si>
     <t>矢贯长阵</t>
   </si>
   <si>
     <t>穿透一击</t>
   </si>
   <si>
-    <t>涅槃</t>
+    <t>七星灯</t>
   </si>
   <si>
     <t>重生</t>
@@ -362,13 +392,19 @@
     <t>淘汰之刃</t>
   </si>
   <si>
-    <t>复制</t>
-  </si>
-  <si>
-    <t>生命汲取</t>
-  </si>
-  <si>
-    <t>逆伤</t>
+    <t>killNow</t>
+  </si>
+  <si>
+    <t>困兽之斗</t>
+  </si>
+  <si>
+    <t>厚积薄发</t>
+  </si>
+  <si>
+    <t>长驱直入</t>
+  </si>
+  <si>
+    <t>push</t>
   </si>
   <si>
     <t>全局技能-投石</t>
@@ -994,7 +1030,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -1004,6 +1040,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1323,23 +1360,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N57"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85"/>
+  <dimension ref="A1:P56"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="15.2477876106195" customWidth="1"/>
-    <col min="2" max="3" width="23.787610619469" customWidth="1"/>
-    <col min="4" max="4" width="45.6637168141593" customWidth="1"/>
-    <col min="5" max="6" width="19.4159292035398" customWidth="1"/>
-    <col min="7" max="7" width="20.5840707964602" customWidth="1"/>
-    <col min="8" max="8" width="32.8318584070796" customWidth="1"/>
-    <col min="9" max="9" width="29.8318584070796" customWidth="1"/>
-    <col min="10" max="10" width="24.5840707964602" customWidth="1"/>
-    <col min="11" max="11" width="31.3362831858407" customWidth="1"/>
-    <col min="12" max="12" width="12.3362831858407" customWidth="1"/>
-    <col min="14" max="14" width="28.6637168141593" customWidth="1"/>
+    <col min="1" max="1" width="15.25" customWidth="1"/>
+    <col min="2" max="3" width="23.7916666666667" customWidth="1"/>
+    <col min="4" max="4" width="45.6666666666667" customWidth="1"/>
+    <col min="5" max="6" width="19.4166666666667" customWidth="1"/>
+    <col min="7" max="7" width="20.5833333333333" customWidth="1"/>
+    <col min="8" max="8" width="32.8333333333333" customWidth="1"/>
+    <col min="9" max="9" width="29.8333333333333" customWidth="1"/>
+    <col min="10" max="10" width="24.5833333333333" customWidth="1"/>
+    <col min="11" max="11" width="42.0583333333333" customWidth="1"/>
+    <col min="12" max="12" width="69.1166666666667" customWidth="1"/>
+    <col min="13" max="13" width="12.3333333333333" customWidth="1"/>
+    <col min="15" max="15" width="28.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1382,101 +1420,119 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" ht="13.9" spans="1:14">
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="K2" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" t="s">
         <v>17</v>
       </c>
-      <c r="F2" t="s">
+      <c r="M2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O2" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="s">
+      <c r="P2" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M2" t="s">
-        <v>18</v>
-      </c>
-      <c r="N2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>33</v>
+      </c>
+      <c r="N3" t="s">
+        <v>34</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="P3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E4">
         <v>120</v>
@@ -1499,22 +1555,25 @@
       <c r="K4">
         <v>1</v>
       </c>
-      <c r="L4">
-        <v>0</v>
+      <c r="L4" t="s">
+        <v>38</v>
       </c>
       <c r="M4">
         <v>0</v>
       </c>
-      <c r="N4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5">
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E5">
         <v>120</v>
@@ -1535,21 +1594,24 @@
         <v>1</v>
       </c>
       <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="L5" t="s">
+        <v>41</v>
       </c>
       <c r="M5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6">
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E6">
         <v>120</v>
@@ -1572,19 +1634,22 @@
       <c r="K6">
         <v>1</v>
       </c>
-      <c r="L6">
-        <v>0</v>
+      <c r="L6" t="s">
+        <v>38</v>
       </c>
       <c r="M6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="N6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7">
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E7">
         <v>120</v>
@@ -1607,19 +1672,22 @@
       <c r="K7">
         <v>1</v>
       </c>
-      <c r="L7">
-        <v>0</v>
+      <c r="L7" t="s">
+        <v>38</v>
       </c>
       <c r="M7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="N7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8">
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E8">
         <v>120</v>
@@ -1642,19 +1710,22 @@
       <c r="K8">
         <v>1</v>
       </c>
-      <c r="L8">
-        <v>0</v>
+      <c r="L8" t="s">
+        <v>38</v>
       </c>
       <c r="M8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="N8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9">
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E9">
         <v>120</v>
@@ -1675,24 +1746,27 @@
         <v>1</v>
       </c>
       <c r="K9">
-        <v>2</v>
-      </c>
-      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="L9" t="s">
+        <v>41</v>
+      </c>
+      <c r="M9">
         <v>3</v>
       </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10">
         <v>10001</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E10">
         <v>120</v>
@@ -1715,19 +1789,22 @@
       <c r="K10">
         <v>1</v>
       </c>
-      <c r="L10">
-        <v>0</v>
+      <c r="L10" t="s">
+        <v>38</v>
       </c>
       <c r="M10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="N10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11">
         <v>10002</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E11">
         <v>120</v>
@@ -1750,19 +1827,22 @@
       <c r="K11">
         <v>1</v>
       </c>
-      <c r="L11">
-        <v>0</v>
+      <c r="L11" t="s">
+        <v>38</v>
       </c>
       <c r="M11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="N11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12">
         <v>10003</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E12">
         <v>120</v>
@@ -1785,19 +1865,22 @@
       <c r="K12">
         <v>1</v>
       </c>
-      <c r="L12">
-        <v>0</v>
+      <c r="L12" t="s">
+        <v>38</v>
       </c>
       <c r="M12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="N12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13">
         <v>10004</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E13">
         <v>120</v>
@@ -1820,19 +1903,22 @@
       <c r="K13">
         <v>1</v>
       </c>
-      <c r="L13">
-        <v>0</v>
+      <c r="L13" t="s">
+        <v>38</v>
       </c>
       <c r="M13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="N13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14">
         <v>10005</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E14">
         <v>120</v>
@@ -1855,19 +1941,22 @@
       <c r="K14">
         <v>1</v>
       </c>
-      <c r="L14">
-        <v>0</v>
+      <c r="L14" t="s">
+        <v>38</v>
       </c>
       <c r="M14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" customFormat="1" spans="1:14">
+      <c r="N14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" spans="1:16">
       <c r="A15">
         <v>10006</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E15">
         <v>120</v>
@@ -1890,19 +1979,22 @@
       <c r="K15">
         <v>1</v>
       </c>
-      <c r="L15">
-        <v>0</v>
+      <c r="L15" t="s">
+        <v>38</v>
       </c>
       <c r="M15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" customFormat="1" spans="1:14">
+      <c r="N15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" spans="1:16">
       <c r="A16">
         <v>10007</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E16">
         <v>120</v>
@@ -1925,19 +2017,22 @@
       <c r="K16">
         <v>1</v>
       </c>
-      <c r="L16">
-        <v>0</v>
+      <c r="L16" t="s">
+        <v>38</v>
       </c>
       <c r="M16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" customFormat="1" spans="1:14">
+      <c r="N16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="1" spans="1:15">
       <c r="A17">
         <v>10008</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E17">
         <v>120</v>
@@ -1960,19 +2055,22 @@
       <c r="K17">
         <v>1</v>
       </c>
-      <c r="L17">
-        <v>0</v>
+      <c r="L17" t="s">
+        <v>38</v>
       </c>
       <c r="M17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" customFormat="1" spans="1:14">
+      <c r="N17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="1" spans="1:15">
       <c r="A18">
         <v>10009</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E18">
         <v>120</v>
@@ -1995,19 +2093,22 @@
       <c r="K18">
         <v>1</v>
       </c>
-      <c r="L18">
-        <v>0</v>
+      <c r="L18" t="s">
+        <v>38</v>
       </c>
       <c r="M18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" customFormat="1" spans="1:14">
+      <c r="N18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" spans="1:15">
       <c r="A19">
         <v>10010</v>
       </c>
       <c r="B19" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E19">
         <v>120</v>
@@ -2030,19 +2131,22 @@
       <c r="K19">
         <v>1</v>
       </c>
-      <c r="L19">
-        <v>0</v>
+      <c r="L19" t="s">
+        <v>38</v>
       </c>
       <c r="M19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="N19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
       <c r="A20">
         <v>10101</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E20">
         <v>120</v>
@@ -2065,19 +2169,22 @@
       <c r="K20">
         <v>1</v>
       </c>
-      <c r="L20">
-        <v>0</v>
+      <c r="L20" t="s">
+        <v>38</v>
       </c>
       <c r="M20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="N20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21">
         <v>10102</v>
       </c>
       <c r="B21" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E21">
         <v>120</v>
@@ -2100,19 +2207,22 @@
       <c r="K21">
         <v>1</v>
       </c>
-      <c r="L21">
-        <v>0</v>
+      <c r="L21" t="s">
+        <v>38</v>
       </c>
       <c r="M21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="N21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
       <c r="A22">
         <v>10103</v>
       </c>
       <c r="B22" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E22">
         <v>120</v>
@@ -2135,19 +2245,22 @@
       <c r="K22">
         <v>1</v>
       </c>
-      <c r="L22">
-        <v>0</v>
+      <c r="L22" t="s">
+        <v>38</v>
       </c>
       <c r="M22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:14">
+      <c r="N22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
       <c r="A23">
         <v>10104</v>
       </c>
       <c r="B23" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E23">
         <v>120</v>
@@ -2170,19 +2283,22 @@
       <c r="K23">
         <v>1</v>
       </c>
-      <c r="L23">
-        <v>0</v>
+      <c r="L23" t="s">
+        <v>38</v>
       </c>
       <c r="M23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:14">
+      <c r="N23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
       <c r="A24">
         <v>10105</v>
       </c>
       <c r="B24" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E24">
         <v>120</v>
@@ -2205,19 +2321,22 @@
       <c r="K24">
         <v>1</v>
       </c>
-      <c r="L24">
-        <v>0</v>
+      <c r="L24" t="s">
+        <v>38</v>
       </c>
       <c r="M24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:14">
+      <c r="N24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
       <c r="A25">
         <v>10106</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E25">
         <v>120</v>
@@ -2240,19 +2359,22 @@
       <c r="K25">
         <v>1</v>
       </c>
-      <c r="L25">
-        <v>0</v>
+      <c r="L25" t="s">
+        <v>38</v>
       </c>
       <c r="M25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:14">
+      <c r="N25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
       <c r="A26">
         <v>10107</v>
       </c>
       <c r="B26" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E26">
         <v>120</v>
@@ -2275,19 +2397,22 @@
       <c r="K26">
         <v>1</v>
       </c>
-      <c r="L26">
-        <v>0</v>
+      <c r="L26" t="s">
+        <v>38</v>
       </c>
       <c r="M26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:14">
+      <c r="N26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
       <c r="A27">
         <v>10108</v>
       </c>
       <c r="B27" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E27">
         <v>120</v>
@@ -2310,19 +2435,22 @@
       <c r="K27">
         <v>1</v>
       </c>
-      <c r="L27">
-        <v>0</v>
+      <c r="L27" t="s">
+        <v>38</v>
       </c>
       <c r="M27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:14">
+      <c r="N27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
       <c r="A28">
         <v>10109</v>
       </c>
       <c r="B28" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="E28">
         <v>120</v>
@@ -2345,19 +2473,22 @@
       <c r="K28">
         <v>1</v>
       </c>
-      <c r="L28">
-        <v>0</v>
+      <c r="L28" t="s">
+        <v>38</v>
       </c>
       <c r="M28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:14">
+      <c r="N28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
       <c r="A29">
         <v>10110</v>
       </c>
       <c r="B29" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E29">
         <v>120</v>
@@ -2380,22 +2511,25 @@
       <c r="K29">
         <v>1</v>
       </c>
-      <c r="L29">
-        <v>0</v>
+      <c r="L29" t="s">
+        <v>38</v>
       </c>
       <c r="M29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:14">
+      <c r="N29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
       <c r="A30">
         <v>100001</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E30">
         <v>120</v>
@@ -2416,25 +2550,28 @@
         <v>0</v>
       </c>
       <c r="K30">
-        <v>2</v>
-      </c>
-      <c r="L30">
+        <v>1</v>
+      </c>
+      <c r="L30" t="s">
+        <v>41</v>
+      </c>
+      <c r="M30">
         <v>6</v>
       </c>
-      <c r="M30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
+      <c r="N30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
       <c r="A31">
         <v>100002</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E31">
         <v>120</v>
@@ -2457,25 +2594,28 @@
       <c r="K31">
         <v>1</v>
       </c>
-      <c r="L31">
-        <v>0</v>
+      <c r="L31" t="s">
+        <v>38</v>
       </c>
       <c r="M31">
         <v>0</v>
       </c>
-      <c r="N31" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
       <c r="A32">
         <v>100003</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E32">
         <v>120</v>
@@ -2496,24 +2636,27 @@
         <v>0</v>
       </c>
       <c r="K32">
-        <v>2</v>
-      </c>
-      <c r="L32">
+        <v>1</v>
+      </c>
+      <c r="L32" t="s">
+        <v>41</v>
+      </c>
+      <c r="M32">
         <v>7</v>
       </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14">
+      <c r="N32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
       <c r="A33">
         <v>100004</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E33">
         <v>120</v>
@@ -2534,24 +2677,27 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>2</v>
-      </c>
-      <c r="L33">
+        <v>1</v>
+      </c>
+      <c r="L33" t="s">
+        <v>41</v>
+      </c>
+      <c r="M33">
         <v>8</v>
       </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14">
+      <c r="N33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
       <c r="A34">
         <v>100005</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E34">
         <v>120</v>
@@ -2574,22 +2720,25 @@
       <c r="K34">
         <v>1</v>
       </c>
-      <c r="L34">
-        <v>0</v>
+      <c r="L34" t="s">
+        <v>38</v>
       </c>
       <c r="M34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:14">
+      <c r="N34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
       <c r="A35">
         <v>100006</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E35">
         <v>120</v>
@@ -2612,22 +2761,25 @@
       <c r="K35">
         <v>1</v>
       </c>
-      <c r="L35">
-        <v>0</v>
+      <c r="L35" t="s">
+        <v>41</v>
       </c>
       <c r="M35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:14">
+      <c r="N35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
       <c r="A36">
         <v>100007</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E36">
         <v>120</v>
@@ -2648,27 +2800,30 @@
         <v>0</v>
       </c>
       <c r="K36">
-        <v>2</v>
-      </c>
-      <c r="L36">
+        <v>1</v>
+      </c>
+      <c r="L36" t="s">
+        <v>41</v>
+      </c>
+      <c r="M36">
         <v>4</v>
       </c>
-      <c r="M36">
-        <v>0</v>
-      </c>
-      <c r="N36" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14">
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
       <c r="A37">
         <v>100008</v>
       </c>
       <c r="B37" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E37">
         <v>120</v>
@@ -2689,24 +2844,27 @@
         <v>0</v>
       </c>
       <c r="K37">
-        <v>2</v>
-      </c>
-      <c r="L37">
+        <v>1</v>
+      </c>
+      <c r="L37" t="s">
+        <v>41</v>
+      </c>
+      <c r="M37">
         <v>5</v>
       </c>
-      <c r="M37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14">
+      <c r="N37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
       <c r="A38">
         <v>100009</v>
       </c>
       <c r="B38" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E38">
         <v>120</v>
@@ -2727,27 +2885,28 @@
         <v>0</v>
       </c>
       <c r="K38">
-        <v>2</v>
-      </c>
-      <c r="L38">
+        <v>1</v>
+      </c>
+      <c r="L38" t="s">
+        <v>41</v>
+      </c>
+      <c r="M38">
         <v>9</v>
       </c>
-      <c r="M38">
-        <v>0</v>
-      </c>
-      <c r="N38" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14">
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38" s="1"/>
+    </row>
+    <row r="39" spans="1:16">
       <c r="A39">
         <v>100010</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E39">
         <v>120</v>
@@ -2768,27 +2927,30 @@
         <v>0</v>
       </c>
       <c r="K39">
-        <v>2</v>
-      </c>
-      <c r="L39">
+        <v>1</v>
+      </c>
+      <c r="L39" t="s">
+        <v>41</v>
+      </c>
+      <c r="M39">
         <v>10</v>
       </c>
-      <c r="M39">
-        <v>0</v>
-      </c>
-      <c r="N39" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14">
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
       <c r="A40">
         <v>100011</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E40">
         <v>120</v>
@@ -2809,24 +2971,27 @@
         <v>0</v>
       </c>
       <c r="K40">
+        <v>1</v>
+      </c>
+      <c r="L40" t="s">
+        <v>41</v>
+      </c>
+      <c r="M40">
         <v>2</v>
       </c>
-      <c r="L40">
-        <v>2</v>
-      </c>
-      <c r="M40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" customFormat="1" spans="1:14">
+      <c r="N40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" customFormat="1" spans="1:16">
       <c r="A41">
         <v>100012</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E41">
         <v>120</v>
@@ -2847,24 +3012,27 @@
         <v>0</v>
       </c>
       <c r="K41">
+        <v>1</v>
+      </c>
+      <c r="L41" t="s">
+        <v>41</v>
+      </c>
+      <c r="M41">
         <v>2</v>
       </c>
-      <c r="L41">
-        <v>2</v>
-      </c>
-      <c r="M41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" customFormat="1" spans="1:14">
+      <c r="N41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" customFormat="1" spans="1:16">
       <c r="A42">
         <v>100013</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E42">
         <v>120</v>
@@ -2885,24 +3053,27 @@
         <v>0</v>
       </c>
       <c r="K42">
-        <v>2</v>
-      </c>
-      <c r="L42">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="L42" t="s">
+        <v>93</v>
       </c>
       <c r="M42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" customFormat="1" spans="1:14">
+      <c r="N42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" customFormat="1" spans="1:16">
       <c r="A43">
         <v>100014</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E43">
         <v>120</v>
@@ -2923,24 +3094,30 @@
         <v>0</v>
       </c>
       <c r="K43">
-        <v>2</v>
-      </c>
-      <c r="L43">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="L43" t="s">
+        <v>96</v>
       </c>
       <c r="M43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" customFormat="1" spans="1:14">
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="P43" s="5">
+        <v>101201</v>
+      </c>
+    </row>
+    <row r="44" customFormat="1" spans="1:16">
       <c r="A44">
         <v>100015</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="E44">
         <v>120</v>
@@ -2963,22 +3140,25 @@
       <c r="K44">
         <v>2</v>
       </c>
-      <c r="L44">
-        <v>2</v>
+      <c r="L44" t="s">
+        <v>99</v>
       </c>
       <c r="M44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" customFormat="1" spans="1:14">
+      <c r="N44">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" customFormat="1" spans="1:16">
       <c r="A45">
         <v>100016</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="E45">
         <v>120</v>
@@ -2999,24 +3179,27 @@
         <v>0</v>
       </c>
       <c r="K45">
-        <v>2</v>
-      </c>
-      <c r="L45">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="L45" t="s">
+        <v>41</v>
       </c>
       <c r="M45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" customFormat="1" spans="1:14">
+        <v>12</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" customFormat="1" spans="1:16">
       <c r="A46">
         <v>100017</v>
       </c>
       <c r="B46" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="E46">
         <v>120</v>
@@ -3037,24 +3220,27 @@
         <v>0</v>
       </c>
       <c r="K46">
+        <v>1</v>
+      </c>
+      <c r="L46" t="s">
+        <v>41</v>
+      </c>
+      <c r="M46">
         <v>2</v>
       </c>
-      <c r="L46">
-        <v>2</v>
-      </c>
-      <c r="M46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" customFormat="1" spans="1:14">
+      <c r="N46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" customFormat="1" spans="1:16">
       <c r="A47">
         <v>100018</v>
       </c>
       <c r="B47" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E47">
         <v>120</v>
@@ -3066,7 +3252,7 @@
         <v>10</v>
       </c>
       <c r="H47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47">
         <v>20</v>
@@ -3075,24 +3261,30 @@
         <v>0</v>
       </c>
       <c r="K47">
-        <v>2</v>
-      </c>
-      <c r="L47">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="L47" t="s">
+        <v>106</v>
       </c>
       <c r="M47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" customFormat="1" spans="1:14">
+        <v>14</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="P47" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" spans="1:16">
       <c r="A48">
         <v>100019</v>
       </c>
       <c r="B48" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="E48">
         <v>120</v>
@@ -3113,24 +3305,27 @@
         <v>0</v>
       </c>
       <c r="K48">
+        <v>1</v>
+      </c>
+      <c r="L48" t="s">
+        <v>41</v>
+      </c>
+      <c r="M48">
         <v>2</v>
       </c>
-      <c r="L48">
-        <v>2</v>
-      </c>
-      <c r="M48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" customFormat="1" spans="1:14">
+      <c r="N48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" customFormat="1" spans="1:16">
       <c r="A49">
         <v>100020</v>
       </c>
       <c r="B49" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C49" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="E49">
         <v>120</v>
@@ -3153,22 +3348,28 @@
       <c r="K49">
         <v>2</v>
       </c>
-      <c r="L49">
-        <v>2</v>
+      <c r="L49" t="s">
+        <v>38</v>
       </c>
       <c r="M49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" customFormat="1" spans="1:14">
+      <c r="N49">
+        <v>5</v>
+      </c>
+      <c r="P49">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="50" customFormat="1" spans="1:16">
       <c r="A50">
         <v>100021</v>
       </c>
       <c r="B50" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="C50" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="E50">
         <v>120</v>
@@ -3189,24 +3390,27 @@
         <v>0</v>
       </c>
       <c r="K50">
-        <v>2</v>
-      </c>
-      <c r="L50">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="L50" t="s">
+        <v>113</v>
       </c>
       <c r="M50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" customFormat="1" spans="1:14">
+      <c r="N50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" customFormat="1" spans="1:16">
       <c r="A51">
         <v>100022</v>
       </c>
       <c r="B51" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="C51" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="E51">
         <v>120</v>
@@ -3218,7 +3422,7 @@
         <v>10</v>
       </c>
       <c r="H51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I51">
         <v>20</v>
@@ -3227,24 +3431,27 @@
         <v>0</v>
       </c>
       <c r="K51">
-        <v>2</v>
-      </c>
-      <c r="L51">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="L51" t="s">
+        <v>38</v>
       </c>
       <c r="M51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" customFormat="1" spans="1:14">
+      <c r="N51">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" customFormat="1" spans="1:16">
       <c r="A52">
         <v>100023</v>
       </c>
       <c r="B52" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="C52" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E52">
         <v>120</v>
@@ -3265,59 +3472,65 @@
         <v>0</v>
       </c>
       <c r="K52">
-        <v>2</v>
-      </c>
-      <c r="L52">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="L52" t="s">
+        <v>117</v>
       </c>
       <c r="M52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" customFormat="1" spans="1:14">
+        <v>13</v>
+      </c>
+      <c r="N52">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
       <c r="A53">
-        <v>100024</v>
+        <v>1001</v>
       </c>
       <c r="B53" t="s">
-        <v>105</v>
-      </c>
-      <c r="C53" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="E53">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="F53">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="G53">
         <v>10</v>
       </c>
       <c r="H53">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="I53">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J53">
         <v>0</v>
       </c>
       <c r="K53">
-        <v>2</v>
-      </c>
-      <c r="L53">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="L53" t="s">
+        <v>41</v>
       </c>
       <c r="M53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14">
+        <v>1001</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16">
       <c r="A54">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B54" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="E54">
         <v>1000</v>
@@ -3326,7 +3539,7 @@
         <v>1000</v>
       </c>
       <c r="G54">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H54">
         <v>100</v>
@@ -3338,24 +3551,24 @@
         <v>0</v>
       </c>
       <c r="K54">
-        <v>2</v>
-      </c>
-      <c r="L54">
-        <v>1001</v>
+        <v>1</v>
+      </c>
+      <c r="L54" t="s">
+        <v>41</v>
       </c>
       <c r="M54">
-        <v>0</v>
-      </c>
-      <c r="N54" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14">
+        <v>1002</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" customFormat="1" spans="1:16">
       <c r="A55">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B55" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="E55">
         <v>1000</v>
@@ -3376,21 +3589,24 @@
         <v>0</v>
       </c>
       <c r="K55">
-        <v>2</v>
-      </c>
-      <c r="L55">
-        <v>1002</v>
+        <v>1</v>
+      </c>
+      <c r="L55" t="s">
+        <v>41</v>
       </c>
       <c r="M55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" customFormat="1" spans="1:14">
+        <v>1003</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16">
       <c r="A56">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B56" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="E56">
         <v>1000</v>
@@ -3402,7 +3618,7 @@
         <v>2</v>
       </c>
       <c r="H56">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -3411,51 +3627,19 @@
         <v>0</v>
       </c>
       <c r="K56">
-        <v>2</v>
-      </c>
-      <c r="L56">
-        <v>1003</v>
+        <v>1</v>
+      </c>
+      <c r="L56" t="s">
+        <v>41</v>
       </c>
       <c r="M56">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:14">
-      <c r="A57">
-        <v>1004</v>
-      </c>
-      <c r="B57" t="s">
-        <v>109</v>
-      </c>
-      <c r="E57">
-        <v>1000</v>
-      </c>
-      <c r="F57">
-        <v>1000</v>
-      </c>
-      <c r="G57">
-        <v>2</v>
-      </c>
-      <c r="H57">
-        <v>1000</v>
-      </c>
-      <c r="I57">
-        <v>0</v>
-      </c>
-      <c r="J57">
-        <v>0</v>
-      </c>
-      <c r="K57">
-        <v>2</v>
-      </c>
-      <c r="L57">
-        <v>0</v>
-      </c>
-      <c r="M57">
-        <v>0</v>
-      </c>
-      <c r="N57" t="s">
-        <v>34</v>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
